--- a/backend/product_master.xlsx
+++ b/backend/product_master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TT51\Desktop\Projects\TNSO-Sticker-Maker\backend\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{414E49E7-AEC9-45DC-998A-B471D72F2E61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2767927-9729-4F8E-ABCB-65A994E48F31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{BE30A5F9-1CB4-4A74-8306-433DDF793BA1}"/>
   </bookViews>
@@ -39,12 +39,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="47">
   <si>
-    <t>in M</t>
-  </si>
-  <si>
-    <t>in mm</t>
-  </si>
-  <si>
     <t>IPTYY-XXXXX</t>
   </si>
   <si>
@@ -199,14 +193,19 @@
     <t>widthUnit</t>
   </si>
   <si>
-    <t xml:space="preserve">lengthUnit
-</t>
-  </si>
-  <si>
     <t>packing</t>
   </si>
   <si>
     <t>lotNo</t>
+  </si>
+  <si>
+    <t>mm</t>
+  </si>
+  <si>
+    <t>M</t>
+  </si>
+  <si>
+    <t>lengthUnit</t>
   </si>
 </sst>
 </file>
@@ -908,7 +907,7 @@
     <tableColumn id="8" xr3:uid="{3ABBBEC3-ACE8-4E12-9A35-0F8272720E24}" name="finish" dataDxfId="5"/>
     <tableColumn id="9" xr3:uid="{A698A5DE-AE7A-421E-95E3-9B1B185FCF8C}" name="thicknessUnit" dataDxfId="4"/>
     <tableColumn id="10" xr3:uid="{A360BD11-B3BE-4141-92E5-E571BA93D913}" name="widthUnit" dataDxfId="3"/>
-    <tableColumn id="11" xr3:uid="{2E94A8F1-5A00-4E6E-B0AC-BF48A89F30A0}" name="lengthUnit_x000a_" dataDxfId="2"/>
+    <tableColumn id="11" xr3:uid="{2E94A8F1-5A00-4E6E-B0AC-BF48A89F30A0}" name="lengthUnit" dataDxfId="2"/>
     <tableColumn id="12" xr3:uid="{BFFE88FD-78E2-403B-BDE9-654174A3DDCA}" name="packing" dataDxfId="1"/>
     <tableColumn id="13" xr3:uid="{0C1C90B8-C7A8-4F44-AC91-A3CB4F22C5D9}" name="lotNo" dataDxfId="0"/>
   </tableColumns>
@@ -1230,42 +1229,42 @@
     <col min="14" max="16384" width="10.6328125" style="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:13" s="3" customFormat="1" ht="39" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B3" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="C3" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="D3" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="C3" s="11" t="s">
+      <c r="E3" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="D3" s="11" t="s">
+      <c r="F3" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="E3" s="12" t="s">
+      <c r="G3" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="F3" s="11" t="s">
+      <c r="H3" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="G3" s="13" t="s">
+      <c r="I3" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="H3" s="14" t="s">
+      <c r="J3" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="I3" s="13" t="s">
+      <c r="K3" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="L3" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="J3" s="13" t="s">
+      <c r="M3" s="15" t="s">
         <v>43</v>
-      </c>
-      <c r="K3" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="L3" s="13" t="s">
-        <v>45</v>
-      </c>
-      <c r="M3" s="15" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="4" spans="2:13" s="8" customFormat="1" ht="12" x14ac:dyDescent="0.35">
@@ -1279,31 +1278,31 @@
         <v>2</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>1</v>
+        <v>44</v>
       </c>
       <c r="J4" s="5" t="s">
-        <v>1</v>
+        <v>44</v>
       </c>
       <c r="K4" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="L4" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="M4" s="10" t="s">
         <v>0</v>
-      </c>
-      <c r="L4" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="M4" s="10" t="s">
-        <v>2</v>
       </c>
     </row>
     <row r="5" spans="2:13" s="8" customFormat="1" ht="12" x14ac:dyDescent="0.35">
@@ -1317,31 +1316,31 @@
         <v>2</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I5" s="5" t="s">
-        <v>1</v>
+        <v>44</v>
       </c>
       <c r="J5" s="5" t="s">
-        <v>1</v>
+        <v>44</v>
       </c>
       <c r="K5" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="L5" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="M5" s="10" t="s">
         <v>0</v>
-      </c>
-      <c r="L5" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="M5" s="10" t="s">
-        <v>2</v>
       </c>
     </row>
     <row r="6" spans="2:13" s="8" customFormat="1" ht="12" x14ac:dyDescent="0.35">
@@ -1355,31 +1354,31 @@
         <v>2</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I6" s="5" t="s">
-        <v>1</v>
+        <v>44</v>
       </c>
       <c r="J6" s="5" t="s">
-        <v>1</v>
+        <v>44</v>
       </c>
       <c r="K6" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="L6" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="M6" s="10" t="s">
         <v>0</v>
-      </c>
-      <c r="L6" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="M6" s="10" t="s">
-        <v>2</v>
       </c>
     </row>
     <row r="7" spans="2:13" s="8" customFormat="1" ht="36" x14ac:dyDescent="0.35">
@@ -1393,31 +1392,31 @@
         <v>4</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F7" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="G7" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="H7" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="I7" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="J7" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="K7" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="L7" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="G7" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="H7" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="I7" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="J7" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="K7" s="5" t="s">
+      <c r="M7" s="10" t="s">
         <v>0</v>
-      </c>
-      <c r="L7" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="M7" s="10" t="s">
-        <v>2</v>
       </c>
     </row>
     <row r="8" spans="2:13" s="8" customFormat="1" ht="36" x14ac:dyDescent="0.35">
@@ -1431,31 +1430,31 @@
         <v>4</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F8" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="G8" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="H8" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="I8" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="J8" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="K8" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="L8" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="G8" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="H8" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="I8" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="J8" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="K8" s="5" t="s">
+      <c r="M8" s="10" t="s">
         <v>0</v>
-      </c>
-      <c r="L8" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="M8" s="10" t="s">
-        <v>2</v>
       </c>
     </row>
     <row r="9" spans="2:13" s="8" customFormat="1" ht="24" x14ac:dyDescent="0.35">
@@ -1469,31 +1468,31 @@
         <v>4</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I9" s="5" t="s">
-        <v>1</v>
+        <v>44</v>
       </c>
       <c r="J9" s="5" t="s">
-        <v>1</v>
+        <v>44</v>
       </c>
       <c r="K9" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="L9" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="M9" s="10" t="s">
         <v>0</v>
-      </c>
-      <c r="L9" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="M9" s="10" t="s">
-        <v>2</v>
       </c>
     </row>
     <row r="10" spans="2:13" s="8" customFormat="1" ht="24" x14ac:dyDescent="0.35">
@@ -1507,31 +1506,31 @@
         <v>4</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F10" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="G10" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="H10" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="G10" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="H10" s="6" t="s">
-        <v>15</v>
-      </c>
       <c r="I10" s="5" t="s">
-        <v>1</v>
+        <v>44</v>
       </c>
       <c r="J10" s="5" t="s">
-        <v>1</v>
+        <v>44</v>
       </c>
       <c r="K10" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="L10" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="M10" s="10" t="s">
         <v>0</v>
-      </c>
-      <c r="L10" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="M10" s="10" t="s">
-        <v>2</v>
       </c>
     </row>
     <row r="11" spans="2:13" s="8" customFormat="1" ht="12" x14ac:dyDescent="0.35">
@@ -1545,31 +1544,31 @@
         <v>4</v>
       </c>
       <c r="E11" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="F11" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="F11" s="7" t="s">
-        <v>19</v>
-      </c>
       <c r="G11" s="7" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I11" s="5" t="s">
-        <v>1</v>
+        <v>44</v>
       </c>
       <c r="J11" s="5" t="s">
-        <v>1</v>
+        <v>44</v>
       </c>
       <c r="K11" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="L11" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="M11" s="10" t="s">
         <v>0</v>
-      </c>
-      <c r="L11" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="M11" s="10" t="s">
-        <v>2</v>
       </c>
     </row>
     <row r="12" spans="2:13" s="8" customFormat="1" ht="12" x14ac:dyDescent="0.35">
@@ -1583,31 +1582,31 @@
         <v>4</v>
       </c>
       <c r="E12" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="F12" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="F12" s="5" t="s">
-        <v>19</v>
-      </c>
       <c r="G12" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="I12" s="5" t="s">
-        <v>1</v>
+        <v>44</v>
       </c>
       <c r="J12" s="5" t="s">
-        <v>1</v>
+        <v>44</v>
       </c>
       <c r="K12" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="L12" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="M12" s="10" t="s">
         <v>0</v>
-      </c>
-      <c r="L12" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="M12" s="10" t="s">
-        <v>2</v>
       </c>
     </row>
     <row r="13" spans="2:13" s="8" customFormat="1" ht="12" x14ac:dyDescent="0.35">
@@ -1621,31 +1620,31 @@
         <v>4</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I13" s="5" t="s">
-        <v>1</v>
+        <v>44</v>
       </c>
       <c r="J13" s="5" t="s">
-        <v>1</v>
+        <v>44</v>
       </c>
       <c r="K13" s="5" t="s">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="L13" s="5" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="M13" s="10" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="14" spans="2:13" s="8" customFormat="1" ht="12" x14ac:dyDescent="0.35">
@@ -1659,31 +1658,31 @@
         <v>4</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G14" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I14" s="5" t="s">
-        <v>1</v>
+        <v>44</v>
       </c>
       <c r="J14" s="5" t="s">
-        <v>1</v>
+        <v>44</v>
       </c>
       <c r="K14" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="L14" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="M14" s="10" t="s">
         <v>0</v>
-      </c>
-      <c r="L14" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="M14" s="10" t="s">
-        <v>2</v>
       </c>
     </row>
     <row r="15" spans="2:13" s="8" customFormat="1" ht="36" x14ac:dyDescent="0.35">
@@ -1697,31 +1696,31 @@
         <v>4</v>
       </c>
       <c r="E15" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F15" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="G15" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="F15" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="G15" s="5" t="s">
-        <v>18</v>
-      </c>
       <c r="H15" s="6" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="I15" s="5" t="s">
-        <v>1</v>
+        <v>44</v>
       </c>
       <c r="J15" s="5" t="s">
-        <v>1</v>
+        <v>44</v>
       </c>
       <c r="K15" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="L15" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="M15" s="10" t="s">
         <v>0</v>
-      </c>
-      <c r="L15" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="M15" s="10" t="s">
-        <v>2</v>
       </c>
     </row>
     <row r="16" spans="2:13" s="8" customFormat="1" ht="24" x14ac:dyDescent="0.35">
@@ -1735,31 +1734,31 @@
         <v>4</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G16" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="I16" s="5" t="s">
-        <v>1</v>
+        <v>44</v>
       </c>
       <c r="J16" s="5" t="s">
-        <v>1</v>
+        <v>44</v>
       </c>
       <c r="K16" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="L16" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="M16" s="10" t="s">
         <v>0</v>
-      </c>
-      <c r="L16" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="M16" s="10" t="s">
-        <v>2</v>
       </c>
     </row>
     <row r="17" spans="2:13" s="8" customFormat="1" ht="24" x14ac:dyDescent="0.35">
@@ -1773,31 +1772,31 @@
         <v>4</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H17" s="6" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="I17" s="5" t="s">
-        <v>1</v>
+        <v>44</v>
       </c>
       <c r="J17" s="5" t="s">
-        <v>1</v>
+        <v>44</v>
       </c>
       <c r="K17" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="L17" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="M17" s="10" t="s">
         <v>0</v>
-      </c>
-      <c r="L17" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="M17" s="10" t="s">
-        <v>2</v>
       </c>
     </row>
     <row r="18" spans="2:13" s="8" customFormat="1" ht="36" x14ac:dyDescent="0.35">
@@ -1811,31 +1810,31 @@
         <v>4</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G18" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H18" s="9" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="I18" s="5" t="s">
-        <v>1</v>
+        <v>44</v>
       </c>
       <c r="J18" s="5" t="s">
-        <v>1</v>
+        <v>44</v>
       </c>
       <c r="K18" s="5" t="s">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="L18" s="5" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="M18" s="10" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="19" spans="2:13" s="8" customFormat="1" ht="24" x14ac:dyDescent="0.35">
@@ -1849,31 +1848,31 @@
         <v>4</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G19" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H19" s="9" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I19" s="5" t="s">
-        <v>1</v>
+        <v>44</v>
       </c>
       <c r="J19" s="5" t="s">
-        <v>1</v>
+        <v>44</v>
       </c>
       <c r="K19" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="L19" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="M19" s="10" t="s">
         <v>0</v>
-      </c>
-      <c r="L19" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="M19" s="10" t="s">
-        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/backend/product_master.xlsx
+++ b/backend/product_master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TT51\Desktop\Projects\TNSO-Sticker-Maker\backend\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2767927-9729-4F8E-ABCB-65A994E48F31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E10C18E-B540-4A57-AAFC-91F123CB3346}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{BE30A5F9-1CB4-4A74-8306-433DDF793BA1}"/>
   </bookViews>
